--- a/00_LATEST_PRESENTED_DECK_AND_DELIVERABLES/ORAN_SPlane_Packets_to_Classification_2026-10-05.xlsx
+++ b/00_LATEST_PRESENTED_DECK_AND_DELIVERABLES/ORAN_SPlane_Packets_to_Classification_2026-10-05.xlsx
@@ -5224,7 +5224,7 @@
       </c>
       <c r="G50" s="37" t="inlineStr">
         <is>
-          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03; MEAS: 36/36 RU logs took the rogue BC as new master].</t>
+          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03]. Measured: 36/36 RU logs recorded it as a new foreign master (candidate); with the real BC still present the RU parent did not change in 5/5 pmc-measured runs, because the BMCA prefers fewer stepsRemoved to the same GM [MEAS; REC].</t>
         </is>
       </c>
       <c r="H50" s="37" t="inlineStr">
@@ -5234,7 +5234,7 @@
       </c>
       <c r="I50" s="37" t="inlineStr">
         <is>
-          <t>Attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
+          <t>If it wins the BMCA or is the only path, the attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
         </is>
       </c>
       <c r="J50" s="6" t="n">
@@ -5312,7 +5312,7 @@
       </c>
       <c r="G51" s="37" t="inlineStr">
         <is>
-          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03; MEAS: 36/36 RU logs took the rogue BC as new master].</t>
+          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03]. Measured: 36/36 RU logs recorded it as a new foreign master (candidate); with the real BC still present the RU parent did not change in 5/5 pmc-measured runs, because the BMCA prefers fewer stepsRemoved to the same GM [MEAS; REC].</t>
         </is>
       </c>
       <c r="H51" s="37" t="inlineStr">
@@ -5322,7 +5322,7 @@
       </c>
       <c r="I51" s="37" t="inlineStr">
         <is>
-          <t>Attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
+          <t>If it wins the BMCA or is the only path, the attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
         </is>
       </c>
       <c r="J51" s="6" t="n">
@@ -5400,7 +5400,7 @@
       </c>
       <c r="G52" s="37" t="inlineStr">
         <is>
-          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03; MEAS: 36/36 RU logs took the rogue BC as new master].</t>
+          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03]. Measured: 36/36 RU logs recorded it as a new foreign master (candidate); with the real BC still present the RU parent did not change in 5/5 pmc-measured runs, because the BMCA prefers fewer stepsRemoved to the same GM [MEAS; REC].</t>
         </is>
       </c>
       <c r="H52" s="37" t="inlineStr">
@@ -5410,7 +5410,7 @@
       </c>
       <c r="I52" s="37" t="inlineStr">
         <is>
-          <t>Attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
+          <t>If it wins the BMCA or is the only path, the attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
         </is>
       </c>
       <c r="J52" s="6" t="n">
@@ -5488,7 +5488,7 @@
       </c>
       <c r="G53" s="37" t="inlineStr">
         <is>
-          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03; MEAS: 36/36 RU logs took the rogue BC as new master].</t>
+          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03]. Measured: 36/36 RU logs recorded it as a new foreign master (candidate); with the real BC still present the RU parent did not change in 5/5 pmc-measured runs, because the BMCA prefers fewer stepsRemoved to the same GM [MEAS; REC].</t>
         </is>
       </c>
       <c r="H53" s="37" t="inlineStr">
@@ -5498,7 +5498,7 @@
       </c>
       <c r="I53" s="37" t="inlineStr">
         <is>
-          <t>Attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
+          <t>If it wins the BMCA or is the only path, the attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
         </is>
       </c>
       <c r="J53" s="6" t="n">
@@ -5576,7 +5576,7 @@
       </c>
       <c r="G54" s="37" t="inlineStr">
         <is>
-          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03; MEAS: 36/36 RU logs took the rogue BC as new master].</t>
+          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03]. Measured: 36/36 RU logs recorded it as a new foreign master (candidate); with the real BC still present the RU parent did not change in 5/5 pmc-measured runs, because the BMCA prefers fewer stepsRemoved to the same GM [MEAS; REC].</t>
         </is>
       </c>
       <c r="H54" s="37" t="inlineStr">
@@ -5586,7 +5586,7 @@
       </c>
       <c r="I54" s="37" t="inlineStr">
         <is>
-          <t>Attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
+          <t>If it wins the BMCA or is the only path, the attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
         </is>
       </c>
       <c r="J54" s="6" t="n">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="G55" s="37" t="inlineStr">
         <is>
-          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03; MEAS: 36/36 RU logs took the rogue BC as new master].</t>
+          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03]. Measured: 36/36 RU logs recorded it as a new foreign master (candidate); with the real BC still present the RU parent did not change in 5/5 pmc-measured runs, because the BMCA prefers fewer stepsRemoved to the same GM [MEAS; REC].</t>
         </is>
       </c>
       <c r="H55" s="37" t="inlineStr">
@@ -5674,7 +5674,7 @@
       </c>
       <c r="I55" s="37" t="inlineStr">
         <is>
-          <t>Attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
+          <t>If it wins the BMCA or is the only path, the attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
         </is>
       </c>
       <c r="J55" s="6" t="n">
@@ -5752,7 +5752,7 @@
       </c>
       <c r="G56" s="37" t="inlineStr">
         <is>
-          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03; MEAS: 36/36 RU logs took the rogue BC as new master].</t>
+          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03]. Measured: 36/36 RU logs recorded it as a new foreign master (candidate); with the real BC still present the RU parent did not change in 5/5 pmc-measured runs, because the BMCA prefers fewer stepsRemoved to the same GM [MEAS; REC].</t>
         </is>
       </c>
       <c r="H56" s="37" t="inlineStr">
@@ -5762,7 +5762,7 @@
       </c>
       <c r="I56" s="37" t="inlineStr">
         <is>
-          <t>Attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
+          <t>If it wins the BMCA or is the only path, the attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
         </is>
       </c>
       <c r="J56" s="6" t="n">
@@ -5840,7 +5840,7 @@
       </c>
       <c r="G57" s="37" t="inlineStr">
         <is>
-          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03; MEAS: 36/36 RU logs took the rogue BC as new master].</t>
+          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03]. Measured: 36/36 RU logs recorded it as a new foreign master (candidate); with the real BC still present the RU parent did not change in 5/5 pmc-measured runs, because the BMCA prefers fewer stepsRemoved to the same GM [MEAS; REC].</t>
         </is>
       </c>
       <c r="H57" s="37" t="inlineStr">
@@ -5850,7 +5850,7 @@
       </c>
       <c r="I57" s="37" t="inlineStr">
         <is>
-          <t>Attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
+          <t>If it wins the BMCA or is the only path, the attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
         </is>
       </c>
       <c r="J57" s="6" t="n">
@@ -5928,7 +5928,7 @@
       </c>
       <c r="G58" s="37" t="inlineStr">
         <is>
-          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03; MEAS: 36/36 RU logs took the rogue BC as new master].</t>
+          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03]. Measured: 36/36 RU logs recorded it as a new foreign master (candidate); with the real BC still present the RU parent did not change in 5/5 pmc-measured runs, because the BMCA prefers fewer stepsRemoved to the same GM [MEAS; REC].</t>
         </is>
       </c>
       <c r="H58" s="37" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="I58" s="37" t="inlineStr">
         <is>
-          <t>Attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
+          <t>If it wins the BMCA or is the only path, the attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
         </is>
       </c>
       <c r="J58" s="6" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="G59" s="37" t="inlineStr">
         <is>
-          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03; MEAS: 36/36 RU logs took the rogue BC as new master].</t>
+          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03]. Measured: 36/36 RU logs recorded it as a new foreign master (candidate); with the real BC still present the RU parent did not change in 5/5 pmc-measured runs, because the BMCA prefers fewer stepsRemoved to the same GM [MEAS; REC].</t>
         </is>
       </c>
       <c r="H59" s="37" t="inlineStr">
@@ -6026,7 +6026,7 @@
       </c>
       <c r="I59" s="37" t="inlineStr">
         <is>
-          <t>Attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
+          <t>If it wins the BMCA or is the only path, the attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
         </is>
       </c>
       <c r="J59" s="6" t="n">
@@ -6104,7 +6104,7 @@
       </c>
       <c r="G60" s="37" t="inlineStr">
         <is>
-          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03; MEAS: 36/36 RU logs took the rogue BC as new master].</t>
+          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03]. Measured: 36/36 RU logs recorded it as a new foreign master (candidate); with the real BC still present the RU parent did not change in 5/5 pmc-measured runs, because the BMCA prefers fewer stepsRemoved to the same GM [MEAS; REC].</t>
         </is>
       </c>
       <c r="H60" s="37" t="inlineStr">
@@ -6114,7 +6114,7 @@
       </c>
       <c r="I60" s="37" t="inlineStr">
         <is>
-          <t>Attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
+          <t>If it wins the BMCA or is the only path, the attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
         </is>
       </c>
       <c r="J60" s="6" t="n">
@@ -6192,7 +6192,7 @@
       </c>
       <c r="G61" s="37" t="inlineStr">
         <is>
-          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03; MEAS: 36/36 RU logs took the rogue BC as new master].</t>
+          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03]. Measured: 36/36 RU logs recorded it as a new foreign master (candidate); with the real BC still present the RU parent did not change in 5/5 pmc-measured runs, because the BMCA prefers fewer stepsRemoved to the same GM [MEAS; REC].</t>
         </is>
       </c>
       <c r="H61" s="37" t="inlineStr">
@@ -6202,7 +6202,7 @@
       </c>
       <c r="I61" s="37" t="inlineStr">
         <is>
-          <t>Attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
+          <t>If it wins the BMCA or is the only path, the attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
         </is>
       </c>
       <c r="J61" s="6" t="n">
@@ -12198,7 +12198,7 @@
       </c>
       <c r="I134" s="37" t="inlineStr">
         <is>
-          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log [MEAS].</t>
+          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log or pmc-measured run [MEAS; REC].</t>
         </is>
       </c>
       <c r="J134" s="6" t="n">
@@ -12282,7 +12282,7 @@
       </c>
       <c r="I135" s="37" t="inlineStr">
         <is>
-          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log [MEAS].</t>
+          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log or pmc-measured run [MEAS; REC].</t>
         </is>
       </c>
       <c r="J135" s="6" t="n">
@@ -12366,7 +12366,7 @@
       </c>
       <c r="I136" s="37" t="inlineStr">
         <is>
-          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log [MEAS].</t>
+          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log or pmc-measured run [MEAS; REC].</t>
         </is>
       </c>
       <c r="J136" s="6" t="n">
@@ -12450,7 +12450,7 @@
       </c>
       <c r="I137" s="37" t="inlineStr">
         <is>
-          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log [MEAS].</t>
+          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log or pmc-measured run [MEAS; REC].</t>
         </is>
       </c>
       <c r="J137" s="6" t="n">
@@ -12534,7 +12534,7 @@
       </c>
       <c r="I138" s="37" t="inlineStr">
         <is>
-          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log [MEAS].</t>
+          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log or pmc-measured run [MEAS; REC].</t>
         </is>
       </c>
       <c r="J138" s="6" t="n">
@@ -12618,7 +12618,7 @@
       </c>
       <c r="I139" s="37" t="inlineStr">
         <is>
-          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log [MEAS].</t>
+          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log or pmc-measured run [MEAS; REC].</t>
         </is>
       </c>
       <c r="J139" s="6" t="n">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="I140" s="37" t="inlineStr">
         <is>
-          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log [MEAS].</t>
+          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log or pmc-measured run [MEAS; REC].</t>
         </is>
       </c>
       <c r="J140" s="6" t="n">
@@ -12786,7 +12786,7 @@
       </c>
       <c r="I141" s="37" t="inlineStr">
         <is>
-          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log [MEAS].</t>
+          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log or pmc-measured run [MEAS; REC].</t>
         </is>
       </c>
       <c r="J141" s="6" t="n">
@@ -12870,7 +12870,7 @@
       </c>
       <c r="I142" s="37" t="inlineStr">
         <is>
-          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log [MEAS].</t>
+          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log or pmc-measured run [MEAS; REC].</t>
         </is>
       </c>
       <c r="J142" s="6" t="n">
@@ -12954,7 +12954,7 @@
       </c>
       <c r="I143" s="37" t="inlineStr">
         <is>
-          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log [MEAS].</t>
+          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log or pmc-measured run [MEAS; REC].</t>
         </is>
       </c>
       <c r="J143" s="6" t="n">
@@ -13038,7 +13038,7 @@
       </c>
       <c r="I144" s="37" t="inlineStr">
         <is>
-          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log [MEAS].</t>
+          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log or pmc-measured run [MEAS; REC].</t>
         </is>
       </c>
       <c r="J144" s="6" t="n">
@@ -13122,7 +13122,7 @@
       </c>
       <c r="I145" s="37" t="inlineStr">
         <is>
-          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log [MEAS].</t>
+          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log or pmc-measured run [MEAS; REC].</t>
         </is>
       </c>
       <c r="J145" s="6" t="n">
@@ -13196,7 +13196,7 @@
       </c>
       <c r="G146" s="37" t="inlineStr">
         <is>
-          <t>O-RU time-properties data set (UTC offset / leap handling) [TS982].</t>
+          <t>O-RU parent selection and time-properties data set (UTC offset / leap handling) [TS982].</t>
         </is>
       </c>
       <c r="H146" s="37" t="inlineStr">
@@ -13206,7 +13206,7 @@
       </c>
       <c r="I146" s="37" t="inlineStr">
         <is>
-          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: no master change; servo reports 3.0 vs 22 per log [MEAS].</t>
+          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: RUs re-parented to the forger (which uses GM-A's identity) in 5/5 pmc-measured runs - invisible in the ptp4l GM-selection line; servo reports 3.0 vs 22 per log [MEAS; REC].</t>
         </is>
       </c>
       <c r="J146" s="6" t="n">
@@ -13280,7 +13280,7 @@
       </c>
       <c r="G147" s="37" t="inlineStr">
         <is>
-          <t>O-RU time-properties data set (UTC offset / leap handling) [TS982].</t>
+          <t>O-RU parent selection and time-properties data set (UTC offset / leap handling) [TS982].</t>
         </is>
       </c>
       <c r="H147" s="37" t="inlineStr">
@@ -13290,7 +13290,7 @@
       </c>
       <c r="I147" s="37" t="inlineStr">
         <is>
-          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: no master change; servo reports 3.0 vs 22 per log [MEAS].</t>
+          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: RUs re-parented to the forger (which uses GM-A's identity) in 5/5 pmc-measured runs - invisible in the ptp4l GM-selection line; servo reports 3.0 vs 22 per log [MEAS; REC].</t>
         </is>
       </c>
       <c r="J147" s="6" t="n">
@@ -13364,7 +13364,7 @@
       </c>
       <c r="G148" s="37" t="inlineStr">
         <is>
-          <t>O-RU time-properties data set (UTC offset / leap handling) [TS982].</t>
+          <t>O-RU parent selection and time-properties data set (UTC offset / leap handling) [TS982].</t>
         </is>
       </c>
       <c r="H148" s="37" t="inlineStr">
@@ -13374,7 +13374,7 @@
       </c>
       <c r="I148" s="37" t="inlineStr">
         <is>
-          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: no master change; servo reports 3.0 vs 22 per log [MEAS].</t>
+          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: RUs re-parented to the forger (which uses GM-A's identity) in 5/5 pmc-measured runs - invisible in the ptp4l GM-selection line; servo reports 3.0 vs 22 per log [MEAS; REC].</t>
         </is>
       </c>
       <c r="J148" s="6" t="n">
@@ -13448,7 +13448,7 @@
       </c>
       <c r="G149" s="37" t="inlineStr">
         <is>
-          <t>O-RU time-properties data set (UTC offset / leap handling) [TS982].</t>
+          <t>O-RU parent selection and time-properties data set (UTC offset / leap handling) [TS982].</t>
         </is>
       </c>
       <c r="H149" s="37" t="inlineStr">
@@ -13458,7 +13458,7 @@
       </c>
       <c r="I149" s="37" t="inlineStr">
         <is>
-          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: no master change; servo reports 3.0 vs 22 per log [MEAS].</t>
+          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: RUs re-parented to the forger (which uses GM-A's identity) in 5/5 pmc-measured runs - invisible in the ptp4l GM-selection line; servo reports 3.0 vs 22 per log [MEAS; REC].</t>
         </is>
       </c>
       <c r="J149" s="6" t="n">
@@ -13532,7 +13532,7 @@
       </c>
       <c r="G150" s="37" t="inlineStr">
         <is>
-          <t>O-RU time-properties data set (UTC offset / leap handling) [TS982].</t>
+          <t>O-RU parent selection and time-properties data set (UTC offset / leap handling) [TS982].</t>
         </is>
       </c>
       <c r="H150" s="37" t="inlineStr">
@@ -13542,7 +13542,7 @@
       </c>
       <c r="I150" s="37" t="inlineStr">
         <is>
-          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: no master change; servo reports 3.0 vs 22 per log [MEAS].</t>
+          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: RUs re-parented to the forger (which uses GM-A's identity) in 5/5 pmc-measured runs - invisible in the ptp4l GM-selection line; servo reports 3.0 vs 22 per log [MEAS; REC].</t>
         </is>
       </c>
       <c r="J150" s="6" t="n">
@@ -13616,7 +13616,7 @@
       </c>
       <c r="G151" s="37" t="inlineStr">
         <is>
-          <t>O-RU time-properties data set (UTC offset / leap handling) [TS982].</t>
+          <t>O-RU parent selection and time-properties data set (UTC offset / leap handling) [TS982].</t>
         </is>
       </c>
       <c r="H151" s="37" t="inlineStr">
@@ -13626,7 +13626,7 @@
       </c>
       <c r="I151" s="37" t="inlineStr">
         <is>
-          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: no master change; servo reports 3.0 vs 22 per log [MEAS].</t>
+          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: RUs re-parented to the forger (which uses GM-A's identity) in 5/5 pmc-measured runs - invisible in the ptp4l GM-selection line; servo reports 3.0 vs 22 per log [MEAS; REC].</t>
         </is>
       </c>
       <c r="J151" s="6" t="n">
@@ -13700,7 +13700,7 @@
       </c>
       <c r="G152" s="37" t="inlineStr">
         <is>
-          <t>O-RU time-properties data set (UTC offset / leap handling) [TS982].</t>
+          <t>O-RU parent selection and time-properties data set (UTC offset / leap handling) [TS982].</t>
         </is>
       </c>
       <c r="H152" s="37" t="inlineStr">
@@ -13710,7 +13710,7 @@
       </c>
       <c r="I152" s="37" t="inlineStr">
         <is>
-          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: no master change; servo reports 3.0 vs 22 per log [MEAS].</t>
+          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: RUs re-parented to the forger (which uses GM-A's identity) in 5/5 pmc-measured runs - invisible in the ptp4l GM-selection line; servo reports 3.0 vs 22 per log [MEAS; REC].</t>
         </is>
       </c>
       <c r="J152" s="6" t="n">
@@ -13784,7 +13784,7 @@
       </c>
       <c r="G153" s="37" t="inlineStr">
         <is>
-          <t>O-RU time-properties data set (UTC offset / leap handling) [TS982].</t>
+          <t>O-RU parent selection and time-properties data set (UTC offset / leap handling) [TS982].</t>
         </is>
       </c>
       <c r="H153" s="37" t="inlineStr">
@@ -13794,7 +13794,7 @@
       </c>
       <c r="I153" s="37" t="inlineStr">
         <is>
-          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: no master change; servo reports 3.0 vs 22 per log [MEAS].</t>
+          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: RUs re-parented to the forger (which uses GM-A's identity) in 5/5 pmc-measured runs - invisible in the ptp4l GM-selection line; servo reports 3.0 vs 22 per log [MEAS; REC].</t>
         </is>
       </c>
       <c r="J153" s="6" t="n">
@@ -13868,7 +13868,7 @@
       </c>
       <c r="G154" s="37" t="inlineStr">
         <is>
-          <t>O-RU time-properties data set (UTC offset / leap handling) [TS982].</t>
+          <t>O-RU parent selection and time-properties data set (UTC offset / leap handling) [TS982].</t>
         </is>
       </c>
       <c r="H154" s="37" t="inlineStr">
@@ -13878,7 +13878,7 @@
       </c>
       <c r="I154" s="37" t="inlineStr">
         <is>
-          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: no master change; servo reports 3.0 vs 22 per log [MEAS].</t>
+          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: RUs re-parented to the forger (which uses GM-A's identity) in 5/5 pmc-measured runs - invisible in the ptp4l GM-selection line; servo reports 3.0 vs 22 per log [MEAS; REC].</t>
         </is>
       </c>
       <c r="J154" s="6" t="n">
@@ -13952,7 +13952,7 @@
       </c>
       <c r="G155" s="37" t="inlineStr">
         <is>
-          <t>O-RU time-properties data set (UTC offset / leap handling) [TS982].</t>
+          <t>O-RU parent selection and time-properties data set (UTC offset / leap handling) [TS982].</t>
         </is>
       </c>
       <c r="H155" s="37" t="inlineStr">
@@ -13962,7 +13962,7 @@
       </c>
       <c r="I155" s="37" t="inlineStr">
         <is>
-          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: no master change; servo reports 3.0 vs 22 per log [MEAS].</t>
+          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: RUs re-parented to the forger (which uses GM-A's identity) in 5/5 pmc-measured runs - invisible in the ptp4l GM-selection line; servo reports 3.0 vs 22 per log [MEAS; REC].</t>
         </is>
       </c>
       <c r="J155" s="6" t="n">
@@ -14036,7 +14036,7 @@
       </c>
       <c r="G156" s="37" t="inlineStr">
         <is>
-          <t>O-RU time-properties data set (UTC offset / leap handling) [TS982].</t>
+          <t>O-RU parent selection and time-properties data set (UTC offset / leap handling) [TS982].</t>
         </is>
       </c>
       <c r="H156" s="37" t="inlineStr">
@@ -14046,7 +14046,7 @@
       </c>
       <c r="I156" s="37" t="inlineStr">
         <is>
-          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: no master change; servo reports 3.0 vs 22 per log [MEAS].</t>
+          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: RUs re-parented to the forger (which uses GM-A's identity) in 5/5 pmc-measured runs - invisible in the ptp4l GM-selection line; servo reports 3.0 vs 22 per log [MEAS; REC].</t>
         </is>
       </c>
       <c r="J156" s="6" t="n">
@@ -14120,7 +14120,7 @@
       </c>
       <c r="G157" s="37" t="inlineStr">
         <is>
-          <t>O-RU time-properties data set (UTC offset / leap handling) [TS982].</t>
+          <t>O-RU parent selection and time-properties data set (UTC offset / leap handling) [TS982].</t>
         </is>
       </c>
       <c r="H157" s="37" t="inlineStr">
@@ -14130,7 +14130,7 @@
       </c>
       <c r="I157" s="37" t="inlineStr">
         <is>
-          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: no master change; servo reports 3.0 vs 22 per log [MEAS].</t>
+          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: RUs re-parented to the forger (which uses GM-A's identity) in 5/5 pmc-measured runs - invisible in the ptp4l GM-selection line; servo reports 3.0 vs 22 per log [MEAS; REC].</t>
         </is>
       </c>
       <c r="J157" s="6" t="n">
@@ -15418,7 +15418,7 @@
       </c>
       <c r="D6" s="40" t="inlineStr">
         <is>
-          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03; MEAS: 36/36 RU logs took the rogue BC as new master].</t>
+          <t>O-RU parent selection - every O-RU behind the inserted clock [TR106 T-SPLANE-03]. Measured: 36/36 RU logs recorded it as a new foreign master (candidate); with the real BC still present the RU parent did not change in 5/5 pmc-measured runs, because the BMCA prefers fewer stepsRemoved to the same GM [MEAS; REC].</t>
         </is>
       </c>
       <c r="E6" s="40" t="inlineStr">
@@ -15428,7 +15428,7 @@
       </c>
       <c r="F6" s="40" t="inlineStr">
         <is>
-          <t>Attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
+          <t>If it wins the BMCA or is the only path, the attacker controls the time relayed to all downstream O-RUs; slaves given inaccurate time [TR106 T-SPLANE-03; R7384 Table 1 false time].</t>
         </is>
       </c>
       <c r="G6" s="18" t="n">
@@ -15540,7 +15540,7 @@
       </c>
       <c r="F8" s="40" t="inlineStr">
         <is>
-          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log [MEAS].</t>
+          <t>Implementation-dependent: from silent discard to stack crash / DoS [R7384 s3.2.11]. Measured: no master change in any RU log or pmc-measured run [MEAS; REC].</t>
         </is>
       </c>
       <c r="G8" s="18" t="n">
@@ -15586,7 +15586,7 @@
       </c>
       <c r="D9" s="40" t="inlineStr">
         <is>
-          <t>O-RU time-properties data set (UTC offset / leap handling) [TS982].</t>
+          <t>O-RU parent selection and time-properties data set (UTC offset / leap handling) [TS982].</t>
         </is>
       </c>
       <c r="E9" s="40" t="inlineStr">
@@ -15596,7 +15596,7 @@
       </c>
       <c r="F9" s="40" t="inlineStr">
         <is>
-          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: no master change; servo reports 3.0 vs 22 per log [MEAS].</t>
+          <t>False time by whole seconds in UTC-derived timing [R7384 Table 1 false time]. Measured: RUs re-parented to the forger (which uses GM-A's identity) in 5/5 pmc-measured runs - invisible in the ptp4l GM-selection line; servo reports 3.0 vs 22 per log [MEAS; REC].</t>
         </is>
       </c>
       <c r="G9" s="18" t="n">
@@ -17120,7 +17120,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B17"/>
+  <dimension ref="A1:B18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -17300,10 +17300,22 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
+          <t>REC</t>
+        </is>
+      </c>
+      <c r="B17" s="44" t="inlineStr">
+        <is>
+          <t>Measured 5 Oct 2026 in the recovery-loop evaluation (03_RECOVERY_LOOP_S-PLANE, control arm, replicates 13-17): pmc -d 24 PARENT_DATA_SET of RU1/RU2 every 0.5 s, same injection mechanisms as the campaign</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
           <t>B6M</t>
         </is>
       </c>
-      <c r="B17" s="44" t="inlineStr">
+      <c r="B18" s="44" t="inlineStr">
         <is>
           <t>Measured in this project: two-laptop crystal comparison, 2 Oct 2026, outputs/B6_two_machine_2026-10-02/run2/DRIFT_REPORT_run2.md (run 2 ESTABLISHED, +21.013 ppm [20.623, 21.403]; run 1 NOT ESTABLISHED, +20.161 ppm; the 0.852 ppm run-to-run difference exceeds either CI). Consumer laptop crystals against an NTP reference - not telecom-class oscillators</t>
         </is>
